--- a/artfynd/A 30497-2024 artfynd.xlsx
+++ b/artfynd/A 30497-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676820</v>
+        <v>118676818</v>
       </c>
       <c r="B3" t="n">
         <v>97763</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575249</v>
+        <v>575202</v>
       </c>
       <c r="R3" t="n">
         <v>6732520</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676818</v>
+        <v>118676819</v>
       </c>
       <c r="B4" t="n">
         <v>97763</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575202</v>
+        <v>575212</v>
       </c>
       <c r="R4" t="n">
-        <v>6732520</v>
+        <v>6732530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676819</v>
+        <v>118676820</v>
       </c>
       <c r="B5" t="n">
         <v>97763</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575212</v>
+        <v>575249</v>
       </c>
       <c r="R5" t="n">
-        <v>6732530</v>
+        <v>6732520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 30497-2024 artfynd.xlsx
+++ b/artfynd/A 30497-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676818</v>
+        <v>118676820</v>
       </c>
       <c r="B3" t="n">
         <v>97763</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575202</v>
+        <v>575249</v>
       </c>
       <c r="R3" t="n">
         <v>6732520</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676819</v>
+        <v>118676818</v>
       </c>
       <c r="B4" t="n">
         <v>97763</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575212</v>
+        <v>575202</v>
       </c>
       <c r="R4" t="n">
-        <v>6732530</v>
+        <v>6732520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676820</v>
+        <v>118676819</v>
       </c>
       <c r="B5" t="n">
         <v>97763</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575249</v>
+        <v>575212</v>
       </c>
       <c r="R5" t="n">
-        <v>6732520</v>
+        <v>6732530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 30497-2024 artfynd.xlsx
+++ b/artfynd/A 30497-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676821</v>
+        <v>118676819</v>
       </c>
       <c r="B2" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575256</v>
+        <v>575212</v>
       </c>
       <c r="R2" t="n">
-        <v>6732490</v>
+        <v>6732530</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676820</v>
+        <v>118676821</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575249</v>
+        <v>575256</v>
       </c>
       <c r="R3" t="n">
-        <v>6732520</v>
+        <v>6732490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676818</v>
+        <v>118676820</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575202</v>
+        <v>575249</v>
       </c>
       <c r="R4" t="n">
         <v>6732520</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676819</v>
+        <v>118676818</v>
       </c>
       <c r="B5" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575212</v>
+        <v>575202</v>
       </c>
       <c r="R5" t="n">
-        <v>6732530</v>
+        <v>6732520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 30497-2024 artfynd.xlsx
+++ b/artfynd/A 30497-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676819</v>
+        <v>118676820</v>
       </c>
       <c r="B2" t="n">
         <v>97770</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575212</v>
+        <v>575249</v>
       </c>
       <c r="R2" t="n">
-        <v>6732530</v>
+        <v>6732520</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676821</v>
+        <v>118676819</v>
       </c>
       <c r="B3" t="n">
         <v>97770</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575256</v>
+        <v>575212</v>
       </c>
       <c r="R3" t="n">
-        <v>6732490</v>
+        <v>6732530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676820</v>
+        <v>118676821</v>
       </c>
       <c r="B4" t="n">
         <v>97770</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575249</v>
+        <v>575256</v>
       </c>
       <c r="R4" t="n">
-        <v>6732520</v>
+        <v>6732490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
